--- a/july 2026/GT_JULY_26/25-07-2026/Salman.xlsx
+++ b/july 2026/GT_JULY_26/25-07-2026/Salman.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F18565-11C2-4ADD-9B7D-233962FA6E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC53A085-758B-4D41-BCAB-9C5513B05F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7124,7 +7124,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -7152,7 +7152,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -8526,7 +8526,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -8554,7 +8554,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -9928,7 +9928,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -9956,7 +9956,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -11330,7 +11330,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -11358,7 +11358,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -12732,7 +12732,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -12760,7 +12760,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -14134,7 +14134,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -14162,7 +14162,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -15536,7 +15536,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -15564,7 +15564,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -16938,7 +16938,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -16966,7 +16966,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -18340,7 +18340,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -18368,7 +18368,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -19742,7 +19742,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -19770,7 +19770,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -23559,7 +23559,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -23587,7 +23587,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -24961,7 +24961,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -24989,7 +24989,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -26363,7 +26363,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -26391,7 +26391,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -27765,7 +27765,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -27793,7 +27793,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -29167,7 +29167,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -29195,7 +29195,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -30569,7 +30569,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -30597,7 +30597,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -31971,7 +31971,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -31999,7 +31999,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -33373,7 +33373,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -33401,7 +33401,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -34775,7 +34775,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -34803,7 +34803,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -36177,7 +36177,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -36205,7 +36205,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -40352,7 +40352,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -40380,7 +40380,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -41754,7 +41754,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -41782,7 +41782,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -43156,7 +43156,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -43184,7 +43184,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -44558,7 +44558,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -44586,7 +44586,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -45960,7 +45960,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -45988,7 +45988,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -47359,7 +47359,7 @@
       <c r="L4" s="384"/>
       <c r="M4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="N4" s="387"/>
       <c r="O4" s="387"/>
@@ -47387,7 +47387,7 @@
       <c r="L5" s="384"/>
       <c r="M5" s="387">
         <f ca="1">M4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="N5" s="383"/>
       <c r="O5" s="383"/>
@@ -53582,7 +53582,7 @@
       <c r="G3" s="379"/>
       <c r="H3" s="376">
         <f ca="1">+'1'!N4:N4</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="I3" s="376"/>
       <c r="J3" s="377"/>
@@ -53625,7 +53625,7 @@
       </c>
       <c r="T4" s="301">
         <f>+'2'!P35</f>
-        <v>18817.269510508475</v>
+        <v>0</v>
       </c>
       <c r="XEX4" t="s">
         <v>105</v>
@@ -54003,19 +54003,19 @@
       </c>
       <c r="H10" s="309">
         <f>+'1'!H19+'2'!H19+'3'!H19+'4'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19+'19'!H19+'20'!H19+'21'!H19+'22'!H19+'23'!H19+'24'!H19+'25'!H19+'26'!H19+'27'!H19+'28'!H19+'29'!H19+'30'!H19</f>
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="I10" s="236">
         <f t="shared" si="0"/>
-        <v>8716.7999999999993</v>
+        <v>2905.6</v>
       </c>
       <c r="J10" s="286">
         <f>+'1'!J19+'2'!J19+'3'!J19+'4'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19+'19'!J19+'20'!J19+'21'!J19+'22'!J19+'23'!J19+'24'!J19+'25'!J19+'26'!J19+'27'!J19+'28'!J19+'29'!J19+'30'!J19</f>
-        <v>697.34400000000005</v>
+        <v>232.44800000000001</v>
       </c>
       <c r="K10" s="286">
         <f>+'1'!K19+'2'!K19+'3'!K19+'4'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19+'11'!K19+'12'!K19+'13'!K19+'14'!K19+'15'!K19+'16'!K19+'17'!K19+'18'!K19+'19'!K19+'20'!K19+'21'!K19+'22'!K19+'23'!K19+'24'!K19+'25'!K19+'26'!K19+'27'!K19+'28'!K19+'29'!K19+'30'!K19</f>
-        <v>305.08800000000002</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L10" s="286">
         <f>+'1'!L19+'2'!L19+'3'!L19+'4'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19+'11'!L19+'12'!L19+'13'!L19+'14'!L19+'15'!L19+'16'!L19+'17'!L19+'18'!L19+'19'!L19+'20'!L19+'21'!L19+'22'!L19+'23'!L19+'24'!L19+'25'!L19+'26'!L19+'27'!L19+'28'!L19+'29'!L19+'30'!L19</f>
@@ -54023,19 +54023,19 @@
       </c>
       <c r="M10" s="230">
         <f t="shared" si="1"/>
-        <v>7714.3679999999995</v>
+        <v>2571.4560000000001</v>
       </c>
       <c r="N10" s="286">
         <f>+'1'!N19+'2'!N19+'3'!N19+'4'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19+'11'!N19+'12'!N19+'13'!N19+'14'!N19+'15'!N19+'16'!N19+'17'!N19+'18'!N19+'19'!N19+'20'!N19+'21'!N19+'22'!N19+'23'!N19+'24'!N19+'25'!N19+'26'!N19+'27'!N19+'28'!N19+'29'!N19+'30'!N19</f>
-        <v>1647.4576271186443</v>
+        <v>549.15254237288138</v>
       </c>
       <c r="O10" s="286">
         <f>+'1'!O19+'2'!O19+'3'!O19+'4'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19+'11'!O19+'12'!O19+'13'!O19+'14'!O19+'15'!O19+'16'!O19+'17'!O19+'18'!O19+'19'!O19+'20'!O19+'21'!O19+'22'!O19+'23'!O19+'24'!O19+'25'!O19+'26'!O19+'27'!O19+'28'!O19+'29'!O19+'30'!O19</f>
-        <v>46.809128135593227</v>
+        <v>15.603042711864408</v>
       </c>
       <c r="P10" s="119">
         <f t="shared" si="2"/>
-        <v>9408.6347552542375</v>
+        <v>3136.2115850847458</v>
       </c>
       <c r="R10" s="299">
         <v>8</v>
@@ -54079,19 +54079,19 @@
       </c>
       <c r="H11" s="309">
         <f>+'1'!H20+'2'!H20+'3'!H20+'4'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20+'19'!H20+'20'!H20+'21'!H20+'22'!H20+'23'!H20+'24'!H20+'25'!H20+'26'!H20+'27'!H20+'28'!H20+'29'!H20+'30'!H20</f>
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="I11" s="236">
         <f t="shared" si="0"/>
-        <v>8716.7999999999993</v>
+        <v>2905.6</v>
       </c>
       <c r="J11" s="286">
         <f>+'1'!J20+'2'!J20+'3'!J20+'4'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20+'19'!J20+'20'!J20+'21'!J20+'22'!J20+'23'!J20+'24'!J20+'25'!J20+'26'!J20+'27'!J20+'28'!J20+'29'!J20+'30'!J20</f>
-        <v>697.34400000000005</v>
+        <v>232.44800000000001</v>
       </c>
       <c r="K11" s="286">
         <f>+'1'!K20+'2'!K20+'3'!K20+'4'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20+'11'!K20+'12'!K20+'13'!K20+'14'!K20+'15'!K20+'16'!K20+'17'!K20+'18'!K20+'19'!K20+'20'!K20+'21'!K20+'22'!K20+'23'!K20+'24'!K20+'25'!K20+'26'!K20+'27'!K20+'28'!K20+'29'!K20+'30'!K20</f>
-        <v>305.08800000000002</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L11" s="286">
         <f>+'1'!L20+'2'!L20+'3'!L20+'4'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20+'11'!L20+'12'!L20+'13'!L20+'14'!L20+'15'!L20+'16'!L20+'17'!L20+'18'!L20+'19'!L20+'20'!L20+'21'!L20+'22'!L20+'23'!L20+'24'!L20+'25'!L20+'26'!L20+'27'!L20+'28'!L20+'29'!L20+'30'!L20</f>
@@ -54099,19 +54099,19 @@
       </c>
       <c r="M11" s="230">
         <f t="shared" si="1"/>
-        <v>7714.3679999999995</v>
+        <v>2571.4560000000001</v>
       </c>
       <c r="N11" s="286">
         <f>+'1'!N20+'2'!N20+'3'!N20+'4'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20+'11'!N20+'12'!N20+'13'!N20+'14'!N20+'15'!N20+'16'!N20+'17'!N20+'18'!N20+'19'!N20+'20'!N20+'21'!N20+'22'!N20+'23'!N20+'24'!N20+'25'!N20+'26'!N20+'27'!N20+'28'!N20+'29'!N20+'30'!N20</f>
-        <v>1647.4576271186443</v>
+        <v>549.15254237288138</v>
       </c>
       <c r="O11" s="286">
         <f>+'1'!O20+'2'!O20+'3'!O20+'4'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20+'11'!O20+'12'!O20+'13'!O20+'14'!O20+'15'!O20+'16'!O20+'17'!O20+'18'!O20+'19'!O20+'20'!O20+'21'!O20+'22'!O20+'23'!O20+'24'!O20+'25'!O20+'26'!O20+'27'!O20+'28'!O20+'29'!O20+'30'!O20</f>
-        <v>46.809128135593227</v>
+        <v>15.603042711864408</v>
       </c>
       <c r="P11" s="119">
         <f t="shared" si="2"/>
-        <v>9408.6347552542375</v>
+        <v>3136.2115850847458</v>
       </c>
       <c r="R11" s="299">
         <v>9</v>
@@ -54155,19 +54155,19 @@
       </c>
       <c r="H12" s="309">
         <f>+'1'!H21+'2'!H21+'3'!H21+'4'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21+'19'!H21+'20'!H21+'21'!H21+'22'!H21+'23'!H21+'24'!H21+'25'!H21+'26'!H21+'27'!H21+'28'!H21+'29'!H21+'30'!H21</f>
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="I12" s="236">
         <f t="shared" si="0"/>
-        <v>8716.7999999999993</v>
+        <v>2905.6</v>
       </c>
       <c r="J12" s="286">
         <f>+'1'!J21+'2'!J21+'3'!J21+'4'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21+'19'!J21+'20'!J21+'21'!J21+'22'!J21+'23'!J21+'24'!J21+'25'!J21+'26'!J21+'27'!J21+'28'!J21+'29'!J21+'30'!J21</f>
-        <v>697.34400000000005</v>
+        <v>232.44800000000001</v>
       </c>
       <c r="K12" s="286">
         <f>+'1'!K21+'2'!K21+'3'!K21+'4'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21+'11'!K21+'12'!K21+'13'!K21+'14'!K21+'15'!K21+'16'!K21+'17'!K21+'18'!K21+'19'!K21+'20'!K21+'21'!K21+'22'!K21+'23'!K21+'24'!K21+'25'!K21+'26'!K21+'27'!K21+'28'!K21+'29'!K21+'30'!K21</f>
-        <v>305.08800000000002</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L12" s="286">
         <f>+'1'!L21+'2'!L21+'3'!L21+'4'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21+'11'!L21+'12'!L21+'13'!L21+'14'!L21+'15'!L21+'16'!L21+'17'!L21+'18'!L21+'19'!L21+'20'!L21+'21'!L21+'22'!L21+'23'!L21+'24'!L21+'25'!L21+'26'!L21+'27'!L21+'28'!L21+'29'!L21+'30'!L21</f>
@@ -54175,19 +54175,19 @@
       </c>
       <c r="M12" s="230">
         <f t="shared" si="1"/>
-        <v>7714.3679999999995</v>
+        <v>2571.4560000000001</v>
       </c>
       <c r="N12" s="286">
         <f>+'1'!N21+'2'!N21+'3'!N21+'4'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21+'11'!N21+'12'!N21+'13'!N21+'14'!N21+'15'!N21+'16'!N21+'17'!N21+'18'!N21+'19'!N21+'20'!N21+'21'!N21+'22'!N21+'23'!N21+'24'!N21+'25'!N21+'26'!N21+'27'!N21+'28'!N21+'29'!N21+'30'!N21</f>
-        <v>1647.4576271186443</v>
+        <v>549.15254237288138</v>
       </c>
       <c r="O12" s="286">
         <f>+'1'!O21+'2'!O21+'3'!O21+'4'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21+'11'!O21+'12'!O21+'13'!O21+'14'!O21+'15'!O21+'16'!O21+'17'!O21+'18'!O21+'19'!O21+'20'!O21+'21'!O21+'22'!O21+'23'!O21+'24'!O21+'25'!O21+'26'!O21+'27'!O21+'28'!O21+'29'!O21+'30'!O21</f>
-        <v>46.809128135593227</v>
+        <v>15.603042711864408</v>
       </c>
       <c r="P12" s="119">
         <f t="shared" si="2"/>
-        <v>9408.6347552542375</v>
+        <v>3136.2115850847458</v>
       </c>
       <c r="R12" s="299">
         <v>10</v>
@@ -54447,19 +54447,19 @@
       </c>
       <c r="H16" s="310">
         <f t="shared" si="3"/>
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="I16" s="114">
         <f t="shared" si="3"/>
-        <v>30347.399999999998</v>
+        <v>12913.800000000001</v>
       </c>
       <c r="J16" s="274">
         <f>SUM(J7:J15)</f>
-        <v>2427.7920000000004</v>
+        <v>1033.104</v>
       </c>
       <c r="K16" s="275">
         <f t="shared" si="3"/>
-        <v>1062.1590000000001</v>
+        <v>451.98300000000006</v>
       </c>
       <c r="L16" s="276">
         <f t="shared" si="3"/>
@@ -54467,19 +54467,19 @@
       </c>
       <c r="M16" s="232">
         <f t="shared" si="3"/>
-        <v>26857.448999999997</v>
+        <v>11428.713000000002</v>
       </c>
       <c r="N16" s="233">
         <f>SUM(N7:N15)</f>
-        <v>5735.5932203389839</v>
+        <v>2440.6779661016944</v>
       </c>
       <c r="O16" s="101">
         <f>SUM(O7:O15)</f>
-        <v>162.96521110169493</v>
+        <v>69.346954830508466</v>
       </c>
       <c r="P16" s="234">
         <f>SUM(P7:P15)</f>
-        <v>32756.007431440674</v>
+        <v>13938.737920932204</v>
       </c>
       <c r="R16" s="299">
         <v>14</v>
@@ -54562,7 +54562,7 @@
       <c r="O19" s="359"/>
       <c r="P19" s="139">
         <f>I16</f>
-        <v>30347.399999999998</v>
+        <v>12913.800000000001</v>
       </c>
       <c r="R19" s="299">
         <v>17</v>
@@ -54594,7 +54594,7 @@
       <c r="O20" s="361"/>
       <c r="P20" s="140">
         <f>+J16</f>
-        <v>2427.7920000000004</v>
+        <v>1033.104</v>
       </c>
       <c r="R20" s="299">
         <v>18</v>
@@ -54626,7 +54626,7 @@
       <c r="O21" s="361"/>
       <c r="P21" s="140">
         <f>+K16+L16</f>
-        <v>1062.1590000000001</v>
+        <v>451.98300000000006</v>
       </c>
       <c r="R21" s="299">
         <v>19</v>
@@ -54659,7 +54659,7 @@
       <c r="O22" s="361"/>
       <c r="P22" s="140">
         <f>P19-P20-P21</f>
-        <v>26857.448999999997</v>
+        <v>11428.713000000002</v>
       </c>
       <c r="R22" s="299">
         <v>20</v>
@@ -54694,7 +54694,7 @@
       </c>
       <c r="P23" s="140">
         <f>+N16</f>
-        <v>5735.5932203389839</v>
+        <v>2440.6779661016944</v>
       </c>
       <c r="R23" s="299">
         <v>21</v>
@@ -54727,7 +54727,7 @@
       <c r="O24" s="363"/>
       <c r="P24" s="140">
         <f>P22+P23</f>
-        <v>32593.042220338983</v>
+        <v>13869.390966101695</v>
       </c>
       <c r="R24" s="299">
         <v>22</v>
@@ -54763,7 +54763,7 @@
       </c>
       <c r="P25" s="140">
         <f>+O16</f>
-        <v>162.96521110169493</v>
+        <v>69.346954830508466</v>
       </c>
       <c r="R25" s="299">
         <v>23</v>
@@ -54784,7 +54784,7 @@
       <c r="O26" s="365"/>
       <c r="P26" s="297">
         <f>+P24+P25</f>
-        <v>32756.007431440677</v>
+        <v>13938.737920932204</v>
       </c>
       <c r="R26" s="299">
         <v>24</v>
@@ -54898,7 +54898,7 @@
       </c>
       <c r="T33" s="304">
         <f>SUM(T3:T32)</f>
-        <v>32756.007431440681</v>
+        <v>13938.737920932204</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.35">
@@ -55036,7 +55036,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -55064,7 +55064,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -56464,7 +56464,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -56492,7 +56492,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -57031,20 +57031,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>80</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>5811.2</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>464.89600000000002</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>203.39200000000002</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -57052,19 +57050,22 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>5142.9120000000003</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>1098.3050847457628</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>31.206085423728815</v>
+        <v>0</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>6272.4231701694916</v>
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>80</v>
       </c>
       <c r="S19" s="269">
         <f>+S18</f>
@@ -57104,20 +57105,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>80</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>5811.2</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>464.89600000000002</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>203.39200000000002</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -57125,23 +57124,26 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>5142.9120000000003</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>1098.3050847457628</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>31.206085423728815</v>
+        <v>0</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>6272.4231701694916</v>
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>80</v>
       </c>
       <c r="R20">
         <f>P20/21</f>
-        <v>298.68681762711867</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -57182,20 +57184,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>80</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>5811.2</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>464.89600000000002</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>203.39200000000002</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -57203,19 +57203,22 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>5142.9120000000003</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>1098.3050847457628</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>31.206085423728815</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>6272.4231701694916</v>
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>80</v>
       </c>
       <c r="S21" s="269">
         <f>+S20</f>
@@ -57469,19 +57472,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>17433.599999999999</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>1394.6880000000001</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>610.17600000000004</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -57489,19 +57492,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>15428.736000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>3294.9152542372885</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>93.618256271186453</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>18817.269510508475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
@@ -57551,7 +57554,7 @@
       <c r="O28" s="359"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>17433.599999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57572,7 +57575,7 @@
       <c r="O29" s="361"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>1394.6880000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57593,7 +57596,7 @@
       <c r="O30" s="361"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>610.17600000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57615,7 +57618,7 @@
       <c r="O31" s="361"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>15428.735999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57639,7 +57642,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>3294.9152542372885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57661,7 +57664,7 @@
       <c r="O33" s="363"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>18723.651254237288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -57686,7 +57689,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>93.618256271186439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -57696,7 +57699,7 @@
       <c r="O35" s="365"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>18817.269510508475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -59276,7 +59279,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -59304,7 +59307,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -60678,7 +60681,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -60706,7 +60709,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
